--- a/data/User_Master.xlsx
+++ b/data/User_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/F&amp;B Sales Dashboard - Project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{435EB669-0B53-404B-9887-A50634BD41E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{730086F9-9A87-43B1-8FFB-8BC9CD7F4240}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{435EB669-0B53-404B-9887-A50634BD41E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{652C854E-E07B-4B04-9021-69BC9B9B429A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B76173A0-443A-4532-A0AF-4EB7DE1D271E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="8">
   <si>
     <t>Admin</t>
   </si>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B85EA44-3A1E-4075-A775-9AEA8A0B328E}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
@@ -529,6 +529,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>112233</v>
+      </c>
+      <c r="B8" s="1">
+        <v>112233</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{1B85EA44-3A1E-4075-A775-9AEA8A0B328E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
